--- a/internal/isbj/testdata/Abrechnung_11-25_0770_anonymized.xlsx
+++ b/internal/isbj/testdata/Abrechnung_11-25_0770_anonymized.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>Am Park 48, 12603 Berlin</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>05.24</t>
+  </si>
+  <si>
+    <t>11/25</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2475,9 @@
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="Z3" s="11" t="inlineStr">
         <is>
           <r>
